--- a/samples/uk2/tls13_gateway/output/test_cases.xlsx
+++ b/samples/uk2/tls13_gateway/output/test_cases.xlsx
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>PERLU_VERIFIKASI</t>
+          <t>COCOK_VEKTOR_RESMI</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2193,13 +2193,13 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TLS 1.3</t>
+          <t>HKDF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Objek uji tersedia &amp; terkonfigurasi: TLS 1.3 | Kunci &amp; data uji ilustratif (bukan material produksi) | Fitur/akses tersedia: protocol_tls13 | Expected value terverifikasi integritasnya (SHA-256 berkas expected/*.json)</t>
+          <t>Objek uji tersedia &amp; terkonfigurasi: HKDF | Kunci &amp; data uji ilustratif (bukan material produksi) | Fitur/akses tersedia: protocol_tls13 | Expected value terverifikasi integritasnya (SHA-256 berkas expected/*.json)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2277,13 +2277,13 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TLS 1.3</t>
+          <t>AES-256-GCM</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Objek uji tersedia &amp; terkonfigurasi: TLS 1.3 | Kunci &amp; data uji ilustratif (bukan material produksi) | Expected value terverifikasi integritasnya (SHA-256 berkas expected/*.json)</t>
+          <t>Objek uji tersedia &amp; terkonfigurasi: AES-256-GCM | Kunci &amp; data uji ilustratif (bukan material produksi) | Expected value terverifikasi integritasnya (SHA-256 berkas expected/*.json)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PERLU_VERIFIKASI</t>
+          <t>COCOK_VEKTOR_RESMI</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -7737,12 +7737,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OBJ:TLS 1.3</t>
+          <t>OBJ:HKDF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kesesuaian TLS 1.3 terhadap standar</t>
+          <t>Kesesuaian HKDF terhadap standar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7772,19 +7772,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TLS 1.3</t>
+          <t>HKDF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OBJ:TLS 1.3</t>
+          <t>OBJ:AES-256-GCM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kesesuaian TLS 1.3 terhadap standar</t>
+          <t>Kesesuaian AES-256-GCM terhadap standar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TLS 1.3</t>
+          <t>AES-256-GCM</t>
         </is>
       </c>
     </row>
